--- a/HoaDonDienTuVaMiSa/Tên Sản Phẩm.xlsx
+++ b/HoaDonDienTuVaMiSa/Tên Sản Phẩm.xlsx
@@ -171,7 +171,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dạ Dày P_GAST 20 gói</t>
+          <t xml:space="preserve">Dung dịch dạ dày P - Gast (Hộp 20 gói)</t>
         </is>
       </c>
     </row>
